--- a/sales_order_forms/009_ice_cube_mold_reorder_form--sales_order_forms.xlsx
+++ b/sales_order_forms/009_ice_cube_mold_reorder_form--sales_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2390,7 +2390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C149"/>
+  <dimension ref="A1:C148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2440,29 +2440,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>product_list_choices</t>
+          <t>product_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -2474,12 +2474,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -2491,29 +2491,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>product_1_choices</t>
+          <t>product_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -2525,29 +2525,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>product_2_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2559,29 +2559,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>submit_choices</t>
+          <t>submit_label_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2593,29 +2593,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>submit_label_choices</t>
+          <t>submit_text_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2627,29 +2627,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>submit_text_choices</t>
+          <t>submit2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2661,29 +2661,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>submit2_choices</t>
+          <t>submit3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2695,29 +2695,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>submit3_choices</t>
+          <t>submit4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2729,29 +2729,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>submit4_choices</t>
+          <t>submit5_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2763,29 +2763,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>submit5_choices</t>
+          <t>submit6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2797,29 +2797,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>submit6_choices</t>
+          <t>submit7_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2831,29 +2831,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>submit7_choices</t>
+          <t>submit8_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2865,29 +2865,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>submit8_choices</t>
+          <t>submit9_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2899,29 +2899,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>submit9_choices</t>
+          <t>submit10_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2933,29 +2933,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>submit10_choices</t>
+          <t>submit11_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2967,29 +2967,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>submit11_choices</t>
+          <t>submit12_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -3001,29 +3001,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>submit12_choices</t>
+          <t>product_3_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -3035,29 +3035,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option_6</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Option 6</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>product_3_choices</t>
+          <t>product_4_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option_7</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Option 7</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -3069,29 +3069,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option_8</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Option 8</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>product_4_choices</t>
+          <t>product_5_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option_9</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Option 9</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -3103,29 +3103,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option_10</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Option 10</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>product_5_choices</t>
+          <t>product_6_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option_11</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Option 11</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -3137,29 +3137,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>option_12</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Option 12</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>product_6_choices</t>
+          <t>product_7_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option_13</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Option 13</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -3171,29 +3171,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>option_14</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Option 14</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>product_7_choices</t>
+          <t>product_8_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>option_15</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Option 15</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -3205,29 +3205,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>option_16</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Option 16</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>product_8_choices</t>
+          <t>product_9_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>option_17</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Option 17</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -3239,29 +3239,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>option_18</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Option 18</t>
+          <t>Option 19</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>product_9_choices</t>
+          <t>product_10_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>option_19</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Option 19</t>
+          <t>Option 20</t>
         </is>
       </c>
     </row>
@@ -3273,29 +3273,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>option_20</t>
+          <t>option_21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Option 20</t>
+          <t>Option 21</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>product_10_choices</t>
+          <t>product_11_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>option_21</t>
+          <t>option_22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Option 21</t>
+          <t>Option 22</t>
         </is>
       </c>
     </row>
@@ -3307,29 +3307,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>option_22</t>
+          <t>option_23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Option 22</t>
+          <t>Option 23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>product_11_choices</t>
+          <t>product_12_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>option_23</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Option 23</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
@@ -3341,29 +3341,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>option_24</t>
+          <t>option_25</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Option 24</t>
+          <t>Option 25</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>product_12_choices</t>
+          <t>product_13_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>option_25</t>
+          <t>option_26</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Option 25</t>
+          <t>Option 26</t>
         </is>
       </c>
     </row>
@@ -3375,29 +3375,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>option_26</t>
+          <t>option_27</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Option 26</t>
+          <t>Option 27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>product_13_choices</t>
+          <t>submit13_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>option_27</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Option 27</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -3409,29 +3409,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>submit13_choices</t>
+          <t>product_14_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>option_28</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Option 28</t>
         </is>
       </c>
     </row>
@@ -3443,29 +3443,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>option_28</t>
+          <t>option_29</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Option 28</t>
+          <t>Option 29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>product_14_choices</t>
+          <t>product_15_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>option_29</t>
+          <t>option_30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Option 29</t>
+          <t>Option 30</t>
         </is>
       </c>
     </row>
@@ -3477,29 +3477,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>option_30</t>
+          <t>option_31</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Option 30</t>
+          <t>Option 31</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>product_15_choices</t>
+          <t>submit14_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>option_31</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Option 31</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -3511,29 +3511,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>submit14_choices</t>
+          <t>product_16_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>option_32</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Option 32</t>
         </is>
       </c>
     </row>
@@ -3545,29 +3545,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>option_32</t>
+          <t>option_33</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Option 32</t>
+          <t>Option 33</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>product_16_choices</t>
+          <t>product_17_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>option_33</t>
+          <t>option_34</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Option 33</t>
+          <t>Option 34</t>
         </is>
       </c>
     </row>
@@ -3579,29 +3579,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>option_34</t>
+          <t>option_35</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Option 34</t>
+          <t>Option 35</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>product_17_choices</t>
+          <t>submit15_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>option_35</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Option 35</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -3613,29 +3613,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>submit15_choices</t>
+          <t>product_18_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>option_36</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Option 36</t>
         </is>
       </c>
     </row>
@@ -3647,29 +3647,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>option_36</t>
+          <t>option_37</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Option 36</t>
+          <t>Option 37</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>product_18_choices</t>
+          <t>product_19_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>option_37</t>
+          <t>option_38</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Option 37</t>
+          <t>Option 38</t>
         </is>
       </c>
     </row>
@@ -3681,29 +3681,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>option_38</t>
+          <t>option_39</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Option 38</t>
+          <t>Option 39</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>product_19_choices</t>
+          <t>product_20_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>option_39</t>
+          <t>option_40</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Option 39</t>
+          <t>Option 40</t>
         </is>
       </c>
     </row>
@@ -3715,29 +3715,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>option_40</t>
+          <t>option_41</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Option 40</t>
+          <t>Option 41</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>product_20_choices</t>
+          <t>submit16_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>option_41</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Option 41</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -3749,29 +3749,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>submit16_choices</t>
+          <t>product_21_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>option_42</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Option 42</t>
         </is>
       </c>
     </row>
@@ -3783,29 +3783,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>option_42</t>
+          <t>option_43</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Option 42</t>
+          <t>Option 43</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>product_21_choices</t>
+          <t>product_22_choices</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>option_43</t>
+          <t>option_44</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Option 43</t>
+          <t>Option 44</t>
         </is>
       </c>
     </row>
@@ -3817,29 +3817,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>option_44</t>
+          <t>option_45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Option 44</t>
+          <t>Option 45</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>product_22_choices</t>
+          <t>product_23_choices</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>option_45</t>
+          <t>option_46</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Option 45</t>
+          <t>Option 46</t>
         </is>
       </c>
     </row>
@@ -3851,29 +3851,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>option_46</t>
+          <t>option_47</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Option 46</t>
+          <t>Option 47</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>product_23_choices</t>
+          <t>product_24_choices</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>option_47</t>
+          <t>option_48</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Option 47</t>
+          <t>Option 48</t>
         </is>
       </c>
     </row>
@@ -3885,29 +3885,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>option_48</t>
+          <t>option_49</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Option 48</t>
+          <t>Option 49</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>product_24_choices</t>
+          <t>product_25_choices</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>option_49</t>
+          <t>option_50</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Option 49</t>
+          <t>Option 50</t>
         </is>
       </c>
     </row>
@@ -3919,29 +3919,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>option_50</t>
+          <t>option_51</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Option 50</t>
+          <t>Option 51</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>product_25_choices</t>
+          <t>submit17_choices</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>option_51</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Option 51</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -3953,29 +3953,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>submit17_choices</t>
+          <t>product_26_choices</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>option_52</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Option 52</t>
         </is>
       </c>
     </row>
@@ -3987,29 +3987,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>option_52</t>
+          <t>option_53</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Option 52</t>
+          <t>Option 53</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>product_26_choices</t>
+          <t>product_27_choices</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>option_53</t>
+          <t>option_54</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Option 53</t>
+          <t>Option 54</t>
         </is>
       </c>
     </row>
@@ -4021,29 +4021,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>option_54</t>
+          <t>option_55</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Option 54</t>
+          <t>Option 55</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>product_27_choices</t>
+          <t>product_28_choices</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>option_55</t>
+          <t>option_56</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Option 55</t>
+          <t>Option 56</t>
         </is>
       </c>
     </row>
@@ -4055,29 +4055,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>option_56</t>
+          <t>option_57</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Option 56</t>
+          <t>Option 57</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>product_28_choices</t>
+          <t>product_29_choices</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>option_57</t>
+          <t>option_58</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Option 57</t>
+          <t>Option 58</t>
         </is>
       </c>
     </row>
@@ -4089,29 +4089,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>option_58</t>
+          <t>option_59</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Option 58</t>
+          <t>Option 59</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>product_29_choices</t>
+          <t>product_30_choices</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>option_59</t>
+          <t>option_60</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Option 59</t>
+          <t>Option 60</t>
         </is>
       </c>
     </row>
@@ -4123,29 +4123,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>option_60</t>
+          <t>option_61</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Option 60</t>
+          <t>Option 61</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>product_30_choices</t>
+          <t>submit18_choices</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>option_61</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Option 61</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -4157,29 +4157,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>submit18_choices</t>
+          <t>product_31_choices</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>option_62</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Option 62</t>
         </is>
       </c>
     </row>
@@ -4191,29 +4191,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>option_62</t>
+          <t>option_63</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Option 62</t>
+          <t>Option 63</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>product_31_choices</t>
+          <t>product_32_choices</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>option_63</t>
+          <t>option_64</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Option 63</t>
+          <t>Option 64</t>
         </is>
       </c>
     </row>
@@ -4225,29 +4225,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>option_64</t>
+          <t>option_65</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Option 64</t>
+          <t>Option 65</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>product_32_choices</t>
+          <t>product_33_choices</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>option_65</t>
+          <t>option_66</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Option 65</t>
+          <t>Option 66</t>
         </is>
       </c>
     </row>
@@ -4259,29 +4259,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>option_66</t>
+          <t>option_67</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Option 66</t>
+          <t>Option 67</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>product_33_choices</t>
+          <t>product_34_choices</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>option_67</t>
+          <t>option_68</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Option 67</t>
+          <t>Option 68</t>
         </is>
       </c>
     </row>
@@ -4293,29 +4293,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>option_68</t>
+          <t>option_69</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Option 68</t>
+          <t>Option 69</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>product_34_choices</t>
+          <t>submit19_choices</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>option_69</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Option 69</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -4327,29 +4327,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>submit19_choices</t>
+          <t>product_35_choices</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>option_70</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Option 70</t>
         </is>
       </c>
     </row>
@@ -4361,29 +4361,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>option_70</t>
+          <t>option_71</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Option 70</t>
+          <t>Option 71</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>product_35_choices</t>
+          <t>product_36_choices</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>option_71</t>
+          <t>option_72</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Option 71</t>
+          <t>Option 72</t>
         </is>
       </c>
     </row>
@@ -4395,29 +4395,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>option_72</t>
+          <t>option_73</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Option 72</t>
+          <t>Option 73</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>product_36_choices</t>
+          <t>product_37_choices</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>option_73</t>
+          <t>option_74</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Option 73</t>
+          <t>Option 74</t>
         </is>
       </c>
     </row>
@@ -4429,29 +4429,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>option_74</t>
+          <t>option_75</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Option 74</t>
+          <t>Option 75</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>product_37_choices</t>
+          <t>product_38_choices</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>option_75</t>
+          <t>option_76</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Option 75</t>
+          <t>Option 76</t>
         </is>
       </c>
     </row>
@@ -4463,29 +4463,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>option_76</t>
+          <t>option_77</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Option 76</t>
+          <t>Option 77</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>product_38_choices</t>
+          <t>product_39_choices</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>option_77</t>
+          <t>option_78</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Option 77</t>
+          <t>Option 78</t>
         </is>
       </c>
     </row>
@@ -4497,29 +4497,29 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>option_78</t>
+          <t>option_79</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Option 78</t>
+          <t>Option 79</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>product_39_choices</t>
+          <t>submit20_choices</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>option_79</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Option 79</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -4531,29 +4531,29 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>submit20_choices</t>
+          <t>product_40_choices</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>option_80</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Option 80</t>
         </is>
       </c>
     </row>
@@ -4565,29 +4565,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>option_80</t>
+          <t>option_81</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Option 80</t>
+          <t>Option 81</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>product_40_choices</t>
+          <t>product_41_choices</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>option_81</t>
+          <t>option_82</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Option 81</t>
+          <t>Option 82</t>
         </is>
       </c>
     </row>
@@ -4599,29 +4599,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>option_82</t>
+          <t>option_83</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Option 82</t>
+          <t>Option 83</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>product_41_choices</t>
+          <t>product_42_choices</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>option_83</t>
+          <t>option_84</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Option 83</t>
+          <t>Option 84</t>
         </is>
       </c>
     </row>
@@ -4633,29 +4633,29 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>option_84</t>
+          <t>option_85</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Option 84</t>
+          <t>Option 85</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>product_42_choices</t>
+          <t>product_43_choices</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>option_85</t>
+          <t>option_86</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Option 85</t>
+          <t>Option 86</t>
         </is>
       </c>
     </row>
@@ -4667,29 +4667,29 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>option_86</t>
+          <t>option_87</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Option 86</t>
+          <t>Option 87</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>product_43_choices</t>
+          <t>product_44_choices</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>option_87</t>
+          <t>option_88</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Option 87</t>
+          <t>Option 88</t>
         </is>
       </c>
     </row>
@@ -4701,29 +4701,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>option_88</t>
+          <t>option_89</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Option 88</t>
+          <t>Option 89</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>product_44_choices</t>
+          <t>submit21_choices</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>option_89</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Option 89</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -4735,29 +4735,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Submit</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>submit21_choices</t>
+          <t>product_45_choices</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>cancel</t>
+          <t>option_90</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>Option 90</t>
         </is>
       </c>
     </row>
@@ -4769,29 +4769,29 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>option_90</t>
+          <t>option_91</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Option 90</t>
+          <t>Option 91</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>product_45_choices</t>
+          <t>product_46_choices</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>option_91</t>
+          <t>option_92</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Option 91</t>
+          <t>Option 92</t>
         </is>
       </c>
     </row>
@@ -4803,29 +4803,29 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>option_92</t>
+          <t>option_93</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Option 92</t>
+          <t>Option 93</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>product_46_choices</t>
+          <t>product_47_choices</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>option_93</t>
+          <t>option_94</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Option 93</t>
+          <t>Option 94</t>
         </is>
       </c>
     </row>
@@ -4837,29 +4837,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>option_94</t>
+          <t>option_95</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Option 94</t>
+          <t>Option 95</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>product_47_choices</t>
+          <t>product_48_choices</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>option_95</t>
+          <t>option_96</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Option 95</t>
+          <t>Option 96</t>
         </is>
       </c>
     </row>
@@ -4871,29 +4871,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>option_96</t>
+          <t>option_97</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Option 96</t>
+          <t>Option 97</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>product_48_choices</t>
+          <t>product_49_choices</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>option_97</t>
+          <t>option_98</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Option 97</t>
+          <t>Option 98</t>
         </is>
       </c>
     </row>
@@ -4905,27 +4905,10 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>option_98</t>
+          <t>option_99</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
-        <is>
-          <t>Option 98</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>product_49_choices</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>option_99</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
         <is>
           <t>Option 99</t>
         </is>
